--- a/cw72022026.xlsx
+++ b/cw72022026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE6B53A-B9FB-FB45-A013-C975A070DC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D62B68F-7FA0-B747-9A16-FC3F30484219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11060" yWindow="2600" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="880" yWindow="1380" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/cw72022026.xlsx
+++ b/cw72022026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D62B68F-7FA0-B747-9A16-FC3F30484219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8A2B7E-7655-2447-9C8A-31298D184501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="1380" windowWidth="29360" windowHeight="16940" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="880" yWindow="600" windowWidth="29360" windowHeight="16080" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -293,7 +293,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M228" totalsRowShown="0">
   <autoFilter ref="A1:M228" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M228">
-    <sortCondition ref="C1:C228"/>
+    <sortCondition ref="A1:A228"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -682,48 +682,57 @@
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="4">
-        <v>0.90540540540540537</v>
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="G2">
+        <v>0.8</v>
       </c>
       <c r="H2" s="5"/>
       <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="15" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="4">
-        <v>0.94594594594594594</v>
+        <v>0.91891891891891897</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
       </c>
       <c r="H3" s="5"/>
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="15" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="4">
-        <v>0.91891891891891897</v>
+        <v>0.90540540540540537</v>
+      </c>
+      <c r="G4">
+        <v>0.14000000000000001</v>
       </c>
       <c r="H4" s="5"/>
       <c r="M4" s="6"/>

--- a/cw72022026.xlsx
+++ b/cw72022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8A2B7E-7655-2447-9C8A-31298D184501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813B07FC-F8D0-A546-8469-057DA773EB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="600" windowWidth="29360" windowHeight="16080" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Surname</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>H250821A</t>
+  </si>
+  <si>
+    <t>Chuma</t>
   </si>
 </sst>
 </file>
@@ -226,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -247,6 +250,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -697,51 +702,72 @@
         <v>0.8</v>
       </c>
       <c r="H2" s="5"/>
+      <c r="J2">
+        <v>0.83</v>
+      </c>
       <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="A3" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="4">
-        <v>0.91891891891891897</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3" s="5"/>
+      <c r="J3">
+        <v>0.32</v>
+      </c>
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="4">
+        <v>0.91891891891891897</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="J4">
+        <v>0.65</v>
+      </c>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4">
         <v>0.90540540540540537</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H4" s="5"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="D5" s="4"/>
       <c r="H5" s="5"/>
+      <c r="J5">
+        <v>0.61</v>
+      </c>
       <c r="M5" s="6"/>
     </row>
     <row r="6" spans="1:13">

--- a/cw72022026.xlsx
+++ b/cw72022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813B07FC-F8D0-A546-8469-057DA773EB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172993EE-BFBC-B341-BB10-8949BB9E81D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="600" windowWidth="29360" windowHeight="16080" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -711,7 +711,8 @@
       <c r="A3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="4">

--- a/cw72022026.xlsx
+++ b/cw72022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172993EE-BFBC-B341-BB10-8949BB9E81D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04094E58-EE9E-344B-9ADE-4DB08B569ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="600" windowWidth="29360" windowHeight="16080" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -250,7 +250,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -705,6 +705,9 @@
       <c r="J2">
         <v>0.83</v>
       </c>
+      <c r="K2">
+        <v>0.79</v>
+      </c>
       <c r="M2" s="6"/>
     </row>
     <row r="3" spans="1:13">
@@ -725,6 +728,9 @@
       <c r="J3">
         <v>0.32</v>
       </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13">
@@ -747,6 +753,9 @@
       <c r="J4">
         <v>0.65</v>
       </c>
+      <c r="K4">
+        <v>0.88</v>
+      </c>
       <c r="M4" s="6"/>
     </row>
     <row r="5" spans="1:13">
@@ -768,6 +777,9 @@
       <c r="H5" s="5"/>
       <c r="J5">
         <v>0.61</v>
+      </c>
+      <c r="K5">
+        <v>0.57999999999999996</v>
       </c>
       <c r="M5" s="6"/>
     </row>

--- a/cw72022026.xlsx
+++ b/cw72022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04094E58-EE9E-344B-9ADE-4DB08B569ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA73BBD2-B9BD-BA48-A961-A3AF1A0CDC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="600" windowWidth="29360" windowHeight="16080" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>

--- a/cw72022026.xlsx
+++ b/cw72022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA73BBD2-B9BD-BA48-A961-A3AF1A0CDC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCD5048-6F37-184F-BA92-4EAFE93561E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="600" windowWidth="29360" windowHeight="16080" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -698,15 +698,26 @@
       <c r="D2" s="4">
         <v>0.94594594594594594</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
       <c r="G2">
         <v>0.8</v>
       </c>
-      <c r="H2" s="5"/>
+      <c r="H2" s="5">
+        <v>0.77</v>
+      </c>
       <c r="J2">
         <v>0.83</v>
       </c>
       <c r="K2">
         <v>0.79</v>
+      </c>
+      <c r="L2">
+        <v>0.95</v>
       </c>
       <c r="M2" s="6"/>
     </row>
@@ -721,14 +732,25 @@
       <c r="D3" s="4">
         <v>0</v>
       </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
-      <c r="H3" s="5"/>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
       <c r="J3">
         <v>0.32</v>
       </c>
       <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" s="6"/>
@@ -746,15 +768,26 @@
       <c r="D4" s="4">
         <v>0.91891891891891897</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0.92</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="5">
+        <v>0.14000000000000001</v>
+      </c>
       <c r="J4">
         <v>0.65</v>
       </c>
       <c r="K4">
         <v>0.88</v>
+      </c>
+      <c r="L4">
+        <v>0.95</v>
       </c>
       <c r="M4" s="6"/>
     </row>
@@ -771,15 +804,26 @@
       <c r="D5" s="4">
         <v>0.90540540540540537</v>
       </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.68</v>
+      </c>
       <c r="G5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="5">
+        <v>0.11</v>
+      </c>
       <c r="J5">
         <v>0.61</v>
       </c>
       <c r="K5">
         <v>0.57999999999999996</v>
+      </c>
+      <c r="L5">
+        <v>0.95</v>
       </c>
       <c r="M5" s="6"/>
     </row>

--- a/cw72022026.xlsx
+++ b/cw72022026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCD5048-6F37-184F-BA92-4EAFE93561E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893AFF2B-98E7-F241-90E5-7A73DFE13AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="600" windowWidth="29360" windowHeight="16080" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -179,15 +179,21 @@
       <name val="Roboto"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="15"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -225,11 +231,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -252,6 +273,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -719,7 +743,10 @@
       <c r="L2">
         <v>0.95</v>
       </c>
-      <c r="M2" s="6"/>
+      <c r="M2" s="18">
+        <f>(((LARGE(D2:F2,1)+LARGE(D2:F2,2))*0.2/2+(LARGE(G2:I2,1)+LARGE(G2:I2,2))*0.5/2+(LARGE(J2:L2,1)+LARGE(J2:L2,2))*0.3/2))</f>
+        <v>0.85949999999999993</v>
+      </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="16" t="s">
@@ -753,7 +780,10 @@
       <c r="L3">
         <v>0</v>
       </c>
-      <c r="M3" s="6"/>
+      <c r="M3" s="18">
+        <f t="shared" ref="M3:M5" si="0">(((LARGE(D3:F3,1)+LARGE(D3:F3,2))*0.2/2+(LARGE(G3:I3,1)+LARGE(G3:I3,2))*0.5/2+(LARGE(J3:L3,1)+LARGE(J3:L3,2))*0.3/2))</f>
+        <v>4.8000000000000001E-2</v>
+      </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="15" t="s">
@@ -775,11 +805,14 @@
         <v>0.92</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="H4" s="5">
         <v>0.14000000000000001</v>
       </c>
+      <c r="I4">
+        <v>0.08</v>
+      </c>
       <c r="J4">
         <v>0.65</v>
       </c>
@@ -789,7 +822,10 @@
       <c r="L4">
         <v>0.95</v>
       </c>
-      <c r="M4" s="6"/>
+      <c r="M4" s="18">
+        <f t="shared" si="0"/>
+        <v>0.66400000000000003</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="17" t="s">
@@ -811,11 +847,14 @@
         <v>0.68</v>
       </c>
       <c r="G5">
-        <v>0.14000000000000001</v>
+        <v>0.69</v>
       </c>
       <c r="H5" s="5">
         <v>0.11</v>
       </c>
+      <c r="I5">
+        <v>0.26</v>
+      </c>
       <c r="J5">
         <v>0.61</v>
       </c>
@@ -825,7 +864,10 @@
       <c r="L5">
         <v>0.95</v>
       </c>
-      <c r="M5" s="6"/>
+      <c r="M5" s="18">
+        <f t="shared" si="0"/>
+        <v>0.63004054054054048</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="8"/>
